--- a/sample/assets_export_2026-03-05_00-58-10.xlsx
+++ b/sample/assets_export_2026-03-05_00-58-10.xlsx
@@ -1,21 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3333" uniqueCount="320">
   <si>
     <t>Masjid/Surau ID</t>
   </si>
@@ -122,52 +134,52 @@
     <t>Pembelian</t>
   </si>
   <si>
+    <t>2,100.00</t>
+  </si>
+  <si>
+    <t>Bilik Mesyuarat</t>
+  </si>
+  <si>
+    <t>En Aziz</t>
+  </si>
+  <si>
+    <t>Timbalan Nazir</t>
+  </si>
+  <si>
+    <t>Sedang Digunakan</t>
+  </si>
+  <si>
+    <t>Baik</t>
+  </si>
+  <si>
+    <t>Tamat</t>
+  </si>
+  <si>
+    <t>22/03/2026</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>PXY57167</t>
+  </si>
+  <si>
+    <t>22/03/2025</t>
+  </si>
+  <si>
+    <t>Syarikat Ego multi task sdn ;;bhd</t>
+  </si>
+  <si>
+    <t>Tiada harga untuk susknilai kerana jumlah bagi setiap Aircond adalah kurang dari RM1500</t>
+  </si>
+  <si>
+    <t>Telah tamat tempuh jaminan</t>
+  </si>
+  <si>
+    <t>MASJI/E/25/039</t>
+  </si>
+  <si>
     <t>2,200.00</t>
-  </si>
-  <si>
-    <t>2,100.00</t>
-  </si>
-  <si>
-    <t>Bilik Mesyuarat</t>
-  </si>
-  <si>
-    <t>En Aziz</t>
-  </si>
-  <si>
-    <t>Timbalan Nazir</t>
-  </si>
-  <si>
-    <t>Sedang Digunakan</t>
-  </si>
-  <si>
-    <t>Baik</t>
-  </si>
-  <si>
-    <t>Tamat</t>
-  </si>
-  <si>
-    <t>22/03/2026</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>PXY57167</t>
-  </si>
-  <si>
-    <t>22/03/2025</t>
-  </si>
-  <si>
-    <t>Syarikat Ego multi task sdn ;;bhd</t>
-  </si>
-  <si>
-    <t>Tiada harga untuk susknilai kerana jumlah bagi setiap Aircond adalah kurang dari RM1500</t>
-  </si>
-  <si>
-    <t>Telah tamat tempuh jaminan</t>
-  </si>
-  <si>
-    <t>MASJI/E/25/039</t>
   </si>
   <si>
     <t>MASJI/BD/23/007</t>
@@ -980,29 +992,180 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="22">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1015,8 +1178,194 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1024,19 +1373,314 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1321,47 +1965,44 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AC175"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="39.99" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="21.138" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="37.705" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="48.274" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="56.558" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="30.564" bestFit="true" customWidth="true" style="0"/>
-    <col min="22" max="22" width="39.99" bestFit="true" customWidth="true" style="0"/>
-    <col min="23" max="23" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="24" max="24" width="24.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="25" max="25" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="26" max="26" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="27" max="27" width="39.99" bestFit="true" customWidth="true" style="0"/>
-    <col min="28" max="28" width="119.114" bestFit="true" customWidth="true" style="0"/>
-    <col min="29" max="29" width="34.135" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="39.9921875" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="37.703125" customWidth="1"/>
+    <col min="6" max="6" width="35.2734375" customWidth="1"/>
+    <col min="7" max="7" width="19.9921875" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.28125" customWidth="1"/>
+    <col min="10" max="10" width="23.421875" customWidth="1"/>
+    <col min="11" max="11" width="29.421875" customWidth="1"/>
+    <col min="12" max="12" width="26.9921875" customWidth="1"/>
+    <col min="13" max="13" width="29.421875" customWidth="1"/>
+    <col min="14" max="14" width="22.28125" customWidth="1"/>
+    <col min="15" max="15" width="19.9921875" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" customWidth="1"/>
+    <col min="17" max="17" width="17.5703125" customWidth="1"/>
+    <col min="18" max="18" width="48.2734375" customWidth="1"/>
+    <col min="19" max="19" width="56.5546875" customWidth="1"/>
+    <col min="20" max="20" width="12.8515625" customWidth="1"/>
+    <col min="21" max="21" width="30.5625" customWidth="1"/>
+    <col min="22" max="22" width="39.9921875" customWidth="1"/>
+    <col min="23" max="23" width="8.140625" customWidth="1"/>
+    <col min="24" max="24" width="24.7109375" customWidth="1"/>
+    <col min="25" max="25" width="23.421875" customWidth="1"/>
+    <col min="26" max="26" width="17.5703125" customWidth="1"/>
+    <col min="27" max="27" width="39.9921875" customWidth="1"/>
+    <col min="28" max="28" width="119.1171875" customWidth="1"/>
+    <col min="29" max="29" width="34.1328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29">
@@ -1475,56 +2116,56 @@
       <c r="G2" t="s">
         <v>34</v>
       </c>
-      <c r="H2" t="s">
-        <v>35</v>
+      <c r="H2" s="2">
+        <v>2200</v>
       </c>
       <c r="I2">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>38</v>
       </c>
-      <c r="N2" t="s">
-        <v>39</v>
-      </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" t="s">
         <v>42</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>43</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>44</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>45</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>46</v>
       </c>
-      <c r="V2" t="s">
+      <c r="AB2" t="s">
         <v>47</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>48</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -1532,7 +2173,7 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
         <v>30</v>
@@ -1550,55 +2191,55 @@
         <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
         <v>36</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>37</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>38</v>
       </c>
-      <c r="N3" t="s">
-        <v>39</v>
-      </c>
       <c r="O3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="s">
+        <v>41</v>
+      </c>
+      <c r="R3" t="s">
         <v>42</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>43</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>44</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>45</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>46</v>
       </c>
-      <c r="V3" t="s">
+      <c r="AB3" t="s">
         <v>47</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>48</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -1624,13 +2265,13 @@
         <v>34</v>
       </c>
       <c r="H4">
-        <v>750.0</v>
+        <v>750</v>
       </c>
       <c r="I4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="s">
         <v>56</v>
@@ -1642,13 +2283,13 @@
         <v>58</v>
       </c>
       <c r="O4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R4" t="s">
         <v>59</v>
@@ -1692,13 +2333,13 @@
         <v>34</v>
       </c>
       <c r="H5">
-        <v>800.0</v>
+        <v>800</v>
       </c>
       <c r="I5">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L5" t="s">
         <v>56</v>
@@ -1710,13 +2351,13 @@
         <v>58</v>
       </c>
       <c r="O5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R5" t="s">
         <v>59</v>
@@ -1760,13 +2401,13 @@
         <v>66</v>
       </c>
       <c r="H6">
-        <v>800.0</v>
+        <v>800</v>
       </c>
       <c r="I6">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L6" t="s">
         <v>56</v>
@@ -1778,13 +2419,13 @@
         <v>58</v>
       </c>
       <c r="O6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R6" t="s">
         <v>67</v>
@@ -1831,10 +2472,10 @@
         <v>72</v>
       </c>
       <c r="I7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L7" t="s">
         <v>73</v>
@@ -1846,13 +2487,13 @@
         <v>58</v>
       </c>
       <c r="O7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R7" t="s">
         <v>74</v>
@@ -1899,10 +2540,10 @@
         <v>72</v>
       </c>
       <c r="I8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L8" t="s">
         <v>73</v>
@@ -1914,13 +2555,13 @@
         <v>58</v>
       </c>
       <c r="O8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R8" t="s">
         <v>74</v>
@@ -1967,10 +2608,10 @@
         <v>72</v>
       </c>
       <c r="I9">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L9" t="s">
         <v>73</v>
@@ -1982,13 +2623,13 @@
         <v>58</v>
       </c>
       <c r="O9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R9" t="s">
         <v>74</v>
@@ -2035,10 +2676,10 @@
         <v>72</v>
       </c>
       <c r="I10">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L10" t="s">
         <v>73</v>
@@ -2050,13 +2691,13 @@
         <v>58</v>
       </c>
       <c r="O10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R10" t="s">
         <v>74</v>
@@ -2103,10 +2744,10 @@
         <v>72</v>
       </c>
       <c r="I11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L11" t="s">
         <v>73</v>
@@ -2118,13 +2759,13 @@
         <v>58</v>
       </c>
       <c r="O11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R11" t="s">
         <v>74</v>
@@ -2171,10 +2812,10 @@
         <v>72</v>
       </c>
       <c r="I12">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L12" t="s">
         <v>73</v>
@@ -2186,13 +2827,13 @@
         <v>58</v>
       </c>
       <c r="O12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R12" t="s">
         <v>74</v>
@@ -2239,10 +2880,10 @@
         <v>72</v>
       </c>
       <c r="I13">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L13" t="s">
         <v>73</v>
@@ -2254,13 +2895,13 @@
         <v>58</v>
       </c>
       <c r="O13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R13" t="s">
         <v>74</v>
@@ -2307,10 +2948,10 @@
         <v>72</v>
       </c>
       <c r="I14">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L14" t="s">
         <v>73</v>
@@ -2322,13 +2963,13 @@
         <v>58</v>
       </c>
       <c r="O14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R14" t="s">
         <v>74</v>
@@ -2375,10 +3016,10 @@
         <v>72</v>
       </c>
       <c r="I15">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L15" t="s">
         <v>73</v>
@@ -2390,13 +3031,13 @@
         <v>58</v>
       </c>
       <c r="O15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R15" t="s">
         <v>74</v>
@@ -2443,10 +3084,10 @@
         <v>72</v>
       </c>
       <c r="I16">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L16" t="s">
         <v>73</v>
@@ -2458,13 +3099,13 @@
         <v>58</v>
       </c>
       <c r="O16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R16" t="s">
         <v>74</v>
@@ -2511,10 +3152,10 @@
         <v>72</v>
       </c>
       <c r="I17">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L17" t="s">
         <v>73</v>
@@ -2526,13 +3167,13 @@
         <v>58</v>
       </c>
       <c r="O17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R17" t="s">
         <v>74</v>
@@ -2579,10 +3220,10 @@
         <v>72</v>
       </c>
       <c r="I18">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L18" t="s">
         <v>73</v>
@@ -2594,13 +3235,13 @@
         <v>58</v>
       </c>
       <c r="O18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R18" t="s">
         <v>74</v>
@@ -2647,10 +3288,10 @@
         <v>72</v>
       </c>
       <c r="I19">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L19" t="s">
         <v>73</v>
@@ -2662,13 +3303,13 @@
         <v>58</v>
       </c>
       <c r="O19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R19" t="s">
         <v>74</v>
@@ -2715,10 +3356,10 @@
         <v>72</v>
       </c>
       <c r="I20">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L20" t="s">
         <v>73</v>
@@ -2730,13 +3371,13 @@
         <v>58</v>
       </c>
       <c r="O20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R20" t="s">
         <v>74</v>
@@ -2783,10 +3424,10 @@
         <v>72</v>
       </c>
       <c r="I21">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L21" t="s">
         <v>73</v>
@@ -2798,13 +3439,13 @@
         <v>58</v>
       </c>
       <c r="O21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R21" t="s">
         <v>74</v>
@@ -2851,10 +3492,10 @@
         <v>72</v>
       </c>
       <c r="I22">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L22" t="s">
         <v>73</v>
@@ -2866,13 +3507,13 @@
         <v>58</v>
       </c>
       <c r="O22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R22" t="s">
         <v>74</v>
@@ -2919,10 +3560,10 @@
         <v>72</v>
       </c>
       <c r="I23">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L23" t="s">
         <v>73</v>
@@ -2934,13 +3575,13 @@
         <v>58</v>
       </c>
       <c r="O23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R23" t="s">
         <v>74</v>
@@ -2987,10 +3628,10 @@
         <v>72</v>
       </c>
       <c r="I24">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L24" t="s">
         <v>73</v>
@@ -3002,13 +3643,13 @@
         <v>58</v>
       </c>
       <c r="O24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R24" t="s">
         <v>74</v>
@@ -3055,10 +3696,10 @@
         <v>72</v>
       </c>
       <c r="I25">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L25" t="s">
         <v>73</v>
@@ -3070,13 +3711,13 @@
         <v>58</v>
       </c>
       <c r="O25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R25" t="s">
         <v>74</v>
@@ -3123,10 +3764,10 @@
         <v>72</v>
       </c>
       <c r="I26">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L26" t="s">
         <v>73</v>
@@ -3138,13 +3779,13 @@
         <v>58</v>
       </c>
       <c r="O26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R26" t="s">
         <v>74</v>
@@ -3191,10 +3832,10 @@
         <v>72</v>
       </c>
       <c r="I27">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L27" t="s">
         <v>73</v>
@@ -3206,13 +3847,13 @@
         <v>58</v>
       </c>
       <c r="O27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R27" t="s">
         <v>74</v>
@@ -3259,10 +3900,10 @@
         <v>72</v>
       </c>
       <c r="I28">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L28" t="s">
         <v>73</v>
@@ -3274,13 +3915,13 @@
         <v>58</v>
       </c>
       <c r="O28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R28" t="s">
         <v>74</v>
@@ -3327,10 +3968,10 @@
         <v>72</v>
       </c>
       <c r="I29">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L29" t="s">
         <v>73</v>
@@ -3342,13 +3983,13 @@
         <v>58</v>
       </c>
       <c r="O29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R29" t="s">
         <v>74</v>
@@ -3395,10 +4036,10 @@
         <v>72</v>
       </c>
       <c r="I30">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L30" t="s">
         <v>73</v>
@@ -3410,13 +4051,13 @@
         <v>58</v>
       </c>
       <c r="O30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R30" t="s">
         <v>74</v>
@@ -3463,10 +4104,10 @@
         <v>72</v>
       </c>
       <c r="I31">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L31" t="s">
         <v>73</v>
@@ -3478,13 +4119,13 @@
         <v>58</v>
       </c>
       <c r="O31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R31" t="s">
         <v>74</v>
@@ -3531,10 +4172,10 @@
         <v>72</v>
       </c>
       <c r="I32">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L32" t="s">
         <v>73</v>
@@ -3546,13 +4187,13 @@
         <v>58</v>
       </c>
       <c r="O32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R32" t="s">
         <v>74</v>
@@ -3599,10 +4240,10 @@
         <v>72</v>
       </c>
       <c r="I33">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L33" t="s">
         <v>73</v>
@@ -3614,13 +4255,13 @@
         <v>58</v>
       </c>
       <c r="O33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R33" t="s">
         <v>74</v>
@@ -3667,10 +4308,10 @@
         <v>72</v>
       </c>
       <c r="I34">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L34" t="s">
         <v>73</v>
@@ -3682,13 +4323,13 @@
         <v>58</v>
       </c>
       <c r="O34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R34" t="s">
         <v>74</v>
@@ -3735,10 +4376,10 @@
         <v>72</v>
       </c>
       <c r="I35">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L35" t="s">
         <v>73</v>
@@ -3750,13 +4391,13 @@
         <v>58</v>
       </c>
       <c r="O35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R35" t="s">
         <v>74</v>
@@ -3803,10 +4444,10 @@
         <v>72</v>
       </c>
       <c r="I36">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L36" t="s">
         <v>73</v>
@@ -3818,13 +4459,13 @@
         <v>58</v>
       </c>
       <c r="O36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R36" t="s">
         <v>74</v>
@@ -3871,10 +4512,10 @@
         <v>72</v>
       </c>
       <c r="I37">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L37" t="s">
         <v>73</v>
@@ -3886,13 +4527,13 @@
         <v>58</v>
       </c>
       <c r="O37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R37" t="s">
         <v>74</v>
@@ -3939,10 +4580,10 @@
         <v>72</v>
       </c>
       <c r="I38">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L38" t="s">
         <v>73</v>
@@ -3954,13 +4595,13 @@
         <v>58</v>
       </c>
       <c r="O38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R38" t="s">
         <v>74</v>
@@ -4007,10 +4648,10 @@
         <v>72</v>
       </c>
       <c r="I39">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L39" t="s">
         <v>73</v>
@@ -4022,13 +4663,13 @@
         <v>58</v>
       </c>
       <c r="O39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R39" t="s">
         <v>74</v>
@@ -4075,10 +4716,10 @@
         <v>72</v>
       </c>
       <c r="I40">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L40" t="s">
         <v>73</v>
@@ -4090,13 +4731,13 @@
         <v>58</v>
       </c>
       <c r="O40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R40" t="s">
         <v>74</v>
@@ -4143,10 +4784,10 @@
         <v>72</v>
       </c>
       <c r="I41">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L41" t="s">
         <v>73</v>
@@ -4158,13 +4799,13 @@
         <v>58</v>
       </c>
       <c r="O41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R41" t="s">
         <v>74</v>
@@ -4211,10 +4852,10 @@
         <v>72</v>
       </c>
       <c r="I42">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L42" t="s">
         <v>73</v>
@@ -4226,13 +4867,13 @@
         <v>58</v>
       </c>
       <c r="O42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R42" t="s">
         <v>74</v>
@@ -4279,10 +4920,10 @@
         <v>72</v>
       </c>
       <c r="I43">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L43" t="s">
         <v>73</v>
@@ -4294,13 +4935,13 @@
         <v>58</v>
       </c>
       <c r="O43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q43" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R43" t="s">
         <v>74</v>
@@ -4347,10 +4988,10 @@
         <v>72</v>
       </c>
       <c r="I44">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K44">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L44" t="s">
         <v>73</v>
@@ -4362,13 +5003,13 @@
         <v>58</v>
       </c>
       <c r="O44" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R44" t="s">
         <v>74</v>
@@ -4415,10 +5056,10 @@
         <v>72</v>
       </c>
       <c r="I45">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L45" t="s">
         <v>73</v>
@@ -4430,13 +5071,13 @@
         <v>58</v>
       </c>
       <c r="O45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R45" t="s">
         <v>74</v>
@@ -4483,10 +5124,10 @@
         <v>72</v>
       </c>
       <c r="I46">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L46" t="s">
         <v>73</v>
@@ -4498,13 +5139,13 @@
         <v>58</v>
       </c>
       <c r="O46" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R46" t="s">
         <v>74</v>
@@ -4551,10 +5192,10 @@
         <v>72</v>
       </c>
       <c r="I47">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L47" t="s">
         <v>73</v>
@@ -4566,13 +5207,13 @@
         <v>58</v>
       </c>
       <c r="O47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R47" t="s">
         <v>74</v>
@@ -4619,10 +5260,10 @@
         <v>72</v>
       </c>
       <c r="I48">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L48" t="s">
         <v>73</v>
@@ -4634,13 +5275,13 @@
         <v>58</v>
       </c>
       <c r="O48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R48" t="s">
         <v>74</v>
@@ -4687,10 +5328,10 @@
         <v>72</v>
       </c>
       <c r="I49">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L49" t="s">
         <v>73</v>
@@ -4702,13 +5343,13 @@
         <v>58</v>
       </c>
       <c r="O49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R49" t="s">
         <v>74</v>
@@ -4755,10 +5396,10 @@
         <v>72</v>
       </c>
       <c r="I50">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K50">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L50" t="s">
         <v>73</v>
@@ -4770,13 +5411,13 @@
         <v>58</v>
       </c>
       <c r="O50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R50" t="s">
         <v>74</v>
@@ -4823,10 +5464,10 @@
         <v>72</v>
       </c>
       <c r="I51">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L51" t="s">
         <v>73</v>
@@ -4838,13 +5479,13 @@
         <v>58</v>
       </c>
       <c r="O51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R51" t="s">
         <v>74</v>
@@ -4891,10 +5532,10 @@
         <v>72</v>
       </c>
       <c r="I52">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L52" t="s">
         <v>73</v>
@@ -4906,13 +5547,13 @@
         <v>58</v>
       </c>
       <c r="O52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R52" t="s">
         <v>74</v>
@@ -4959,10 +5600,10 @@
         <v>72</v>
       </c>
       <c r="I53">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L53" t="s">
         <v>73</v>
@@ -4974,13 +5615,13 @@
         <v>58</v>
       </c>
       <c r="O53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R53" t="s">
         <v>74</v>
@@ -5027,10 +5668,10 @@
         <v>72</v>
       </c>
       <c r="I54">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L54" t="s">
         <v>73</v>
@@ -5042,13 +5683,13 @@
         <v>58</v>
       </c>
       <c r="O54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R54" t="s">
         <v>74</v>
@@ -5095,10 +5736,10 @@
         <v>72</v>
       </c>
       <c r="I55">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L55" t="s">
         <v>73</v>
@@ -5110,13 +5751,13 @@
         <v>58</v>
       </c>
       <c r="O55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R55" t="s">
         <v>74</v>
@@ -5163,10 +5804,10 @@
         <v>72</v>
       </c>
       <c r="I56">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L56" t="s">
         <v>73</v>
@@ -5178,13 +5819,13 @@
         <v>58</v>
       </c>
       <c r="O56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R56" t="s">
         <v>74</v>
@@ -5231,10 +5872,10 @@
         <v>72</v>
       </c>
       <c r="I57">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L57" t="s">
         <v>73</v>
@@ -5246,13 +5887,13 @@
         <v>58</v>
       </c>
       <c r="O57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R57" t="s">
         <v>74</v>
@@ -5299,10 +5940,10 @@
         <v>72</v>
       </c>
       <c r="I58">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K58">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L58" t="s">
         <v>73</v>
@@ -5314,13 +5955,13 @@
         <v>58</v>
       </c>
       <c r="O58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R58" t="s">
         <v>74</v>
@@ -5367,10 +6008,10 @@
         <v>72</v>
       </c>
       <c r="I59">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L59" t="s">
         <v>73</v>
@@ -5382,13 +6023,13 @@
         <v>58</v>
       </c>
       <c r="O59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R59" t="s">
         <v>74</v>
@@ -5435,10 +6076,10 @@
         <v>72</v>
       </c>
       <c r="I60">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L60" t="s">
         <v>73</v>
@@ -5450,13 +6091,13 @@
         <v>58</v>
       </c>
       <c r="O60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R60" t="s">
         <v>74</v>
@@ -5503,10 +6144,10 @@
         <v>72</v>
       </c>
       <c r="I61">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K61">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L61" t="s">
         <v>73</v>
@@ -5518,13 +6159,13 @@
         <v>58</v>
       </c>
       <c r="O61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P61" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R61" t="s">
         <v>74</v>
@@ -5571,10 +6212,10 @@
         <v>72</v>
       </c>
       <c r="I62">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K62">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L62" t="s">
         <v>73</v>
@@ -5586,13 +6227,13 @@
         <v>58</v>
       </c>
       <c r="O62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R62" t="s">
         <v>74</v>
@@ -5639,10 +6280,10 @@
         <v>72</v>
       </c>
       <c r="I63">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K63">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L63" t="s">
         <v>73</v>
@@ -5654,13 +6295,13 @@
         <v>58</v>
       </c>
       <c r="O63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R63" t="s">
         <v>74</v>
@@ -5707,10 +6348,10 @@
         <v>72</v>
       </c>
       <c r="I64">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L64" t="s">
         <v>73</v>
@@ -5722,13 +6363,13 @@
         <v>58</v>
       </c>
       <c r="O64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R64" t="s">
         <v>74</v>
@@ -5775,10 +6416,10 @@
         <v>72</v>
       </c>
       <c r="I65">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K65">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L65" t="s">
         <v>73</v>
@@ -5790,13 +6431,13 @@
         <v>58</v>
       </c>
       <c r="O65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P65" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R65" t="s">
         <v>74</v>
@@ -5843,10 +6484,10 @@
         <v>72</v>
       </c>
       <c r="I66">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K66">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L66" t="s">
         <v>73</v>
@@ -5858,13 +6499,13 @@
         <v>58</v>
       </c>
       <c r="O66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P66" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R66" t="s">
         <v>74</v>
@@ -5911,10 +6552,10 @@
         <v>72</v>
       </c>
       <c r="I67">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K67">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L67" t="s">
         <v>73</v>
@@ -5926,13 +6567,13 @@
         <v>58</v>
       </c>
       <c r="O67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R67" t="s">
         <v>74</v>
@@ -5979,10 +6620,10 @@
         <v>72</v>
       </c>
       <c r="I68">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K68">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L68" t="s">
         <v>73</v>
@@ -5994,13 +6635,13 @@
         <v>58</v>
       </c>
       <c r="O68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R68" t="s">
         <v>74</v>
@@ -6047,10 +6688,10 @@
         <v>72</v>
       </c>
       <c r="I69">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K69">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L69" t="s">
         <v>73</v>
@@ -6062,13 +6703,13 @@
         <v>58</v>
       </c>
       <c r="O69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P69" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q69" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R69" t="s">
         <v>74</v>
@@ -6115,10 +6756,10 @@
         <v>72</v>
       </c>
       <c r="I70">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K70">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L70" t="s">
         <v>73</v>
@@ -6130,13 +6771,13 @@
         <v>58</v>
       </c>
       <c r="O70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q70" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R70" t="s">
         <v>74</v>
@@ -6183,10 +6824,10 @@
         <v>72</v>
       </c>
       <c r="I71">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K71">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L71" t="s">
         <v>73</v>
@@ -6198,13 +6839,13 @@
         <v>58</v>
       </c>
       <c r="O71" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P71" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q71" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R71" t="s">
         <v>74</v>
@@ -6251,10 +6892,10 @@
         <v>72</v>
       </c>
       <c r="I72">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K72">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L72" t="s">
         <v>73</v>
@@ -6266,13 +6907,13 @@
         <v>58</v>
       </c>
       <c r="O72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P72" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q72" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R72" t="s">
         <v>74</v>
@@ -6319,10 +6960,10 @@
         <v>72</v>
       </c>
       <c r="I73">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K73">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L73" t="s">
         <v>73</v>
@@ -6334,13 +6975,13 @@
         <v>58</v>
       </c>
       <c r="O73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P73" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q73" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R73" t="s">
         <v>74</v>
@@ -6387,10 +7028,10 @@
         <v>72</v>
       </c>
       <c r="I74">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L74" t="s">
         <v>73</v>
@@ -6402,13 +7043,13 @@
         <v>58</v>
       </c>
       <c r="O74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q74" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R74" t="s">
         <v>74</v>
@@ -6455,10 +7096,10 @@
         <v>72</v>
       </c>
       <c r="I75">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K75">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L75" t="s">
         <v>73</v>
@@ -6470,13 +7111,13 @@
         <v>58</v>
       </c>
       <c r="O75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P75" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q75" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R75" t="s">
         <v>74</v>
@@ -6523,10 +7164,10 @@
         <v>72</v>
       </c>
       <c r="I76">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K76">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L76" t="s">
         <v>73</v>
@@ -6538,13 +7179,13 @@
         <v>58</v>
       </c>
       <c r="O76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R76" t="s">
         <v>74</v>
@@ -6591,10 +7232,10 @@
         <v>72</v>
       </c>
       <c r="I77">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K77">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L77" t="s">
         <v>73</v>
@@ -6606,13 +7247,13 @@
         <v>58</v>
       </c>
       <c r="O77" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R77" t="s">
         <v>74</v>
@@ -6659,10 +7300,10 @@
         <v>72</v>
       </c>
       <c r="I78">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K78">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L78" t="s">
         <v>73</v>
@@ -6674,13 +7315,13 @@
         <v>58</v>
       </c>
       <c r="O78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P78" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q78" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R78" t="s">
         <v>74</v>
@@ -6727,10 +7368,10 @@
         <v>72</v>
       </c>
       <c r="I79">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K79">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L79" t="s">
         <v>73</v>
@@ -6742,13 +7383,13 @@
         <v>58</v>
       </c>
       <c r="O79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P79" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q79" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R79" t="s">
         <v>74</v>
@@ -6795,10 +7436,10 @@
         <v>72</v>
       </c>
       <c r="I80">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K80">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L80" t="s">
         <v>73</v>
@@ -6810,13 +7451,13 @@
         <v>58</v>
       </c>
       <c r="O80" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P80" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q80" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R80" t="s">
         <v>74</v>
@@ -6863,10 +7504,10 @@
         <v>72</v>
       </c>
       <c r="I81">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K81">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L81" t="s">
         <v>73</v>
@@ -6878,13 +7519,13 @@
         <v>58</v>
       </c>
       <c r="O81" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P81" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q81" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R81" t="s">
         <v>74</v>
@@ -6931,10 +7572,10 @@
         <v>72</v>
       </c>
       <c r="I82">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K82">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L82" t="s">
         <v>73</v>
@@ -6946,13 +7587,13 @@
         <v>58</v>
       </c>
       <c r="O82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P82" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R82" t="s">
         <v>74</v>
@@ -6999,10 +7640,10 @@
         <v>72</v>
       </c>
       <c r="I83">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K83">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L83" t="s">
         <v>73</v>
@@ -7014,13 +7655,13 @@
         <v>58</v>
       </c>
       <c r="O83" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q83" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R83" t="s">
         <v>74</v>
@@ -7067,10 +7708,10 @@
         <v>72</v>
       </c>
       <c r="I84">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K84">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L84" t="s">
         <v>73</v>
@@ -7082,13 +7723,13 @@
         <v>58</v>
       </c>
       <c r="O84" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P84" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q84" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R84" t="s">
         <v>74</v>
@@ -7135,10 +7776,10 @@
         <v>72</v>
       </c>
       <c r="I85">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K85">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L85" t="s">
         <v>73</v>
@@ -7150,13 +7791,13 @@
         <v>58</v>
       </c>
       <c r="O85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P85" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q85" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R85" t="s">
         <v>74</v>
@@ -7203,10 +7844,10 @@
         <v>72</v>
       </c>
       <c r="I86">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K86">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L86" t="s">
         <v>73</v>
@@ -7218,13 +7859,13 @@
         <v>58</v>
       </c>
       <c r="O86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P86" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q86" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R86" t="s">
         <v>74</v>
@@ -7271,10 +7912,10 @@
         <v>72</v>
       </c>
       <c r="I87">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K87">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L87" t="s">
         <v>73</v>
@@ -7286,13 +7927,13 @@
         <v>58</v>
       </c>
       <c r="O87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P87" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q87" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R87" t="s">
         <v>74</v>
@@ -7339,10 +7980,10 @@
         <v>72</v>
       </c>
       <c r="I88">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K88">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L88" t="s">
         <v>73</v>
@@ -7354,13 +7995,13 @@
         <v>58</v>
       </c>
       <c r="O88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q88" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R88" t="s">
         <v>74</v>
@@ -7407,10 +8048,10 @@
         <v>72</v>
       </c>
       <c r="I89">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K89">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L89" t="s">
         <v>73</v>
@@ -7422,13 +8063,13 @@
         <v>58</v>
       </c>
       <c r="O89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P89" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q89" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R89" t="s">
         <v>74</v>
@@ -7475,10 +8116,10 @@
         <v>72</v>
       </c>
       <c r="I90">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K90">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L90" t="s">
         <v>73</v>
@@ -7490,13 +8131,13 @@
         <v>58</v>
       </c>
       <c r="O90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P90" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q90" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R90" t="s">
         <v>74</v>
@@ -7543,10 +8184,10 @@
         <v>72</v>
       </c>
       <c r="I91">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K91">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L91" t="s">
         <v>73</v>
@@ -7558,13 +8199,13 @@
         <v>58</v>
       </c>
       <c r="O91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P91" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q91" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R91" t="s">
         <v>74</v>
@@ -7611,10 +8252,10 @@
         <v>72</v>
       </c>
       <c r="I92">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K92">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L92" t="s">
         <v>73</v>
@@ -7626,13 +8267,13 @@
         <v>58</v>
       </c>
       <c r="O92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P92" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q92" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R92" t="s">
         <v>74</v>
@@ -7679,10 +8320,10 @@
         <v>72</v>
       </c>
       <c r="I93">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K93">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L93" t="s">
         <v>73</v>
@@ -7694,13 +8335,13 @@
         <v>58</v>
       </c>
       <c r="O93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P93" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q93" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R93" t="s">
         <v>74</v>
@@ -7747,10 +8388,10 @@
         <v>72</v>
       </c>
       <c r="I94">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K94">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L94" t="s">
         <v>73</v>
@@ -7762,13 +8403,13 @@
         <v>58</v>
       </c>
       <c r="O94" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P94" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q94" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R94" t="s">
         <v>74</v>
@@ -7815,10 +8456,10 @@
         <v>72</v>
       </c>
       <c r="I95">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K95">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L95" t="s">
         <v>73</v>
@@ -7830,13 +8471,13 @@
         <v>58</v>
       </c>
       <c r="O95" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P95" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q95" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R95" t="s">
         <v>74</v>
@@ -7883,10 +8524,10 @@
         <v>72</v>
       </c>
       <c r="I96">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K96">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L96" t="s">
         <v>73</v>
@@ -7898,13 +8539,13 @@
         <v>58</v>
       </c>
       <c r="O96" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P96" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q96" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R96" t="s">
         <v>74</v>
@@ -7951,10 +8592,10 @@
         <v>72</v>
       </c>
       <c r="I97">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K97">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L97" t="s">
         <v>73</v>
@@ -7966,13 +8607,13 @@
         <v>58</v>
       </c>
       <c r="O97" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P97" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q97" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R97" t="s">
         <v>74</v>
@@ -8019,10 +8660,10 @@
         <v>72</v>
       </c>
       <c r="I98">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K98">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L98" t="s">
         <v>73</v>
@@ -8034,13 +8675,13 @@
         <v>58</v>
       </c>
       <c r="O98" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q98" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R98" t="s">
         <v>74</v>
@@ -8087,10 +8728,10 @@
         <v>72</v>
       </c>
       <c r="I99">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K99">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L99" t="s">
         <v>73</v>
@@ -8102,13 +8743,13 @@
         <v>58</v>
       </c>
       <c r="O99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P99" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q99" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R99" t="s">
         <v>74</v>
@@ -8155,10 +8796,10 @@
         <v>72</v>
       </c>
       <c r="I100">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K100">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L100" t="s">
         <v>73</v>
@@ -8170,13 +8811,13 @@
         <v>58</v>
       </c>
       <c r="O100" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P100" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q100" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R100" t="s">
         <v>74</v>
@@ -8223,10 +8864,10 @@
         <v>72</v>
       </c>
       <c r="I101">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K101">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L101" t="s">
         <v>73</v>
@@ -8238,13 +8879,13 @@
         <v>58</v>
       </c>
       <c r="O101" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P101" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q101" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R101" t="s">
         <v>74</v>
@@ -8291,10 +8932,10 @@
         <v>72</v>
       </c>
       <c r="I102">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K102">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L102" t="s">
         <v>73</v>
@@ -8306,13 +8947,13 @@
         <v>58</v>
       </c>
       <c r="O102" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P102" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q102" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R102" t="s">
         <v>74</v>
@@ -8359,10 +9000,10 @@
         <v>72</v>
       </c>
       <c r="I103">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K103">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L103" t="s">
         <v>73</v>
@@ -8374,13 +9015,13 @@
         <v>58</v>
       </c>
       <c r="O103" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P103" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q103" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R103" t="s">
         <v>74</v>
@@ -8427,10 +9068,10 @@
         <v>72</v>
       </c>
       <c r="I104">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K104">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L104" t="s">
         <v>73</v>
@@ -8442,13 +9083,13 @@
         <v>58</v>
       </c>
       <c r="O104" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P104" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q104" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R104" t="s">
         <v>74</v>
@@ -8495,10 +9136,10 @@
         <v>72</v>
       </c>
       <c r="I105">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K105">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L105" t="s">
         <v>73</v>
@@ -8510,13 +9151,13 @@
         <v>58</v>
       </c>
       <c r="O105" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P105" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q105" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R105" t="s">
         <v>74</v>
@@ -8563,10 +9204,10 @@
         <v>72</v>
       </c>
       <c r="I106">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K106">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L106" t="s">
         <v>73</v>
@@ -8578,13 +9219,13 @@
         <v>58</v>
       </c>
       <c r="O106" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P106" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q106" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R106" t="s">
         <v>74</v>
@@ -8631,10 +9272,10 @@
         <v>72</v>
       </c>
       <c r="I107">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K107">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L107" t="s">
         <v>73</v>
@@ -8646,13 +9287,13 @@
         <v>58</v>
       </c>
       <c r="O107" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P107" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q107" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R107" t="s">
         <v>74</v>
@@ -8699,10 +9340,10 @@
         <v>72</v>
       </c>
       <c r="I108">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K108">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L108" t="s">
         <v>73</v>
@@ -8714,13 +9355,13 @@
         <v>58</v>
       </c>
       <c r="O108" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P108" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q108" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R108" t="s">
         <v>74</v>
@@ -8767,10 +9408,10 @@
         <v>72</v>
       </c>
       <c r="I109">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K109">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L109" t="s">
         <v>73</v>
@@ -8782,13 +9423,13 @@
         <v>58</v>
       </c>
       <c r="O109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P109" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q109" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R109" t="s">
         <v>74</v>
@@ -8835,10 +9476,10 @@
         <v>72</v>
       </c>
       <c r="I110">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K110">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L110" t="s">
         <v>73</v>
@@ -8850,13 +9491,13 @@
         <v>58</v>
       </c>
       <c r="O110" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P110" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q110" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R110" t="s">
         <v>74</v>
@@ -8903,10 +9544,10 @@
         <v>72</v>
       </c>
       <c r="I111">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K111">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L111" t="s">
         <v>73</v>
@@ -8918,13 +9559,13 @@
         <v>58</v>
       </c>
       <c r="O111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P111" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q111" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R111" t="s">
         <v>74</v>
@@ -8971,10 +9612,10 @@
         <v>72</v>
       </c>
       <c r="I112">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K112">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L112" t="s">
         <v>73</v>
@@ -8986,13 +9627,13 @@
         <v>58</v>
       </c>
       <c r="O112" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P112" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q112" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R112" t="s">
         <v>74</v>
@@ -9039,10 +9680,10 @@
         <v>72</v>
       </c>
       <c r="I113">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K113">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L113" t="s">
         <v>73</v>
@@ -9054,13 +9695,13 @@
         <v>58</v>
       </c>
       <c r="O113" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P113" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q113" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R113" t="s">
         <v>74</v>
@@ -9107,10 +9748,10 @@
         <v>72</v>
       </c>
       <c r="I114">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K114">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L114" t="s">
         <v>73</v>
@@ -9122,13 +9763,13 @@
         <v>58</v>
       </c>
       <c r="O114" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P114" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q114" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R114" t="s">
         <v>74</v>
@@ -9175,10 +9816,10 @@
         <v>72</v>
       </c>
       <c r="I115">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K115">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L115" t="s">
         <v>73</v>
@@ -9190,13 +9831,13 @@
         <v>58</v>
       </c>
       <c r="O115" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P115" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q115" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R115" t="s">
         <v>74</v>
@@ -9243,10 +9884,10 @@
         <v>72</v>
       </c>
       <c r="I116">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K116">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L116" t="s">
         <v>73</v>
@@ -9258,13 +9899,13 @@
         <v>58</v>
       </c>
       <c r="O116" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P116" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q116" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R116" t="s">
         <v>74</v>
@@ -9311,10 +9952,10 @@
         <v>72</v>
       </c>
       <c r="I117">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K117">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L117" t="s">
         <v>73</v>
@@ -9326,13 +9967,13 @@
         <v>58</v>
       </c>
       <c r="O117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P117" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q117" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R117" t="s">
         <v>74</v>
@@ -9379,10 +10020,10 @@
         <v>72</v>
       </c>
       <c r="I118">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K118">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L118" t="s">
         <v>73</v>
@@ -9394,13 +10035,13 @@
         <v>58</v>
       </c>
       <c r="O118" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P118" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q118" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R118" t="s">
         <v>74</v>
@@ -9447,10 +10088,10 @@
         <v>72</v>
       </c>
       <c r="I119">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K119">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L119" t="s">
         <v>73</v>
@@ -9462,13 +10103,13 @@
         <v>58</v>
       </c>
       <c r="O119" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q119" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R119" t="s">
         <v>74</v>
@@ -9515,10 +10156,10 @@
         <v>72</v>
       </c>
       <c r="I120">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K120">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L120" t="s">
         <v>73</v>
@@ -9530,13 +10171,13 @@
         <v>58</v>
       </c>
       <c r="O120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P120" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q120" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R120" t="s">
         <v>74</v>
@@ -9583,10 +10224,10 @@
         <v>72</v>
       </c>
       <c r="I121">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K121">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L121" t="s">
         <v>73</v>
@@ -9598,13 +10239,13 @@
         <v>58</v>
       </c>
       <c r="O121" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P121" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q121" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R121" t="s">
         <v>74</v>
@@ -9651,10 +10292,10 @@
         <v>72</v>
       </c>
       <c r="I122">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K122">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L122" t="s">
         <v>73</v>
@@ -9666,13 +10307,13 @@
         <v>58</v>
       </c>
       <c r="O122" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P122" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q122" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R122" t="s">
         <v>74</v>
@@ -9719,10 +10360,10 @@
         <v>72</v>
       </c>
       <c r="I123">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K123">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L123" t="s">
         <v>73</v>
@@ -9734,13 +10375,13 @@
         <v>58</v>
       </c>
       <c r="O123" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P123" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q123" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R123" t="s">
         <v>74</v>
@@ -9787,10 +10428,10 @@
         <v>72</v>
       </c>
       <c r="I124">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K124">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L124" t="s">
         <v>73</v>
@@ -9802,13 +10443,13 @@
         <v>58</v>
       </c>
       <c r="O124" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P124" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q124" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R124" t="s">
         <v>74</v>
@@ -9855,10 +10496,10 @@
         <v>72</v>
       </c>
       <c r="I125">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K125">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L125" t="s">
         <v>73</v>
@@ -9870,13 +10511,13 @@
         <v>58</v>
       </c>
       <c r="O125" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P125" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q125" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R125" t="s">
         <v>74</v>
@@ -9923,10 +10564,10 @@
         <v>72</v>
       </c>
       <c r="I126">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K126">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L126" t="s">
         <v>73</v>
@@ -9938,13 +10579,13 @@
         <v>58</v>
       </c>
       <c r="O126" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P126" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q126" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R126" t="s">
         <v>74</v>
@@ -9991,10 +10632,10 @@
         <v>72</v>
       </c>
       <c r="I127">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K127">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L127" t="s">
         <v>73</v>
@@ -10006,13 +10647,13 @@
         <v>58</v>
       </c>
       <c r="O127" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P127" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q127" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R127" t="s">
         <v>74</v>
@@ -10059,10 +10700,10 @@
         <v>72</v>
       </c>
       <c r="I128">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K128">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L128" t="s">
         <v>73</v>
@@ -10074,13 +10715,13 @@
         <v>58</v>
       </c>
       <c r="O128" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P128" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q128" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R128" t="s">
         <v>74</v>
@@ -10127,10 +10768,10 @@
         <v>72</v>
       </c>
       <c r="I129">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K129">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L129" t="s">
         <v>73</v>
@@ -10142,13 +10783,13 @@
         <v>58</v>
       </c>
       <c r="O129" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P129" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q129" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R129" t="s">
         <v>74</v>
@@ -10195,10 +10836,10 @@
         <v>72</v>
       </c>
       <c r="I130">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K130">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L130" t="s">
         <v>73</v>
@@ -10210,13 +10851,13 @@
         <v>58</v>
       </c>
       <c r="O130" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P130" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q130" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R130" t="s">
         <v>74</v>
@@ -10263,10 +10904,10 @@
         <v>72</v>
       </c>
       <c r="I131">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K131">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L131" t="s">
         <v>73</v>
@@ -10278,13 +10919,13 @@
         <v>58</v>
       </c>
       <c r="O131" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P131" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q131" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R131" t="s">
         <v>74</v>
@@ -10331,10 +10972,10 @@
         <v>72</v>
       </c>
       <c r="I132">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K132">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L132" t="s">
         <v>73</v>
@@ -10346,13 +10987,13 @@
         <v>58</v>
       </c>
       <c r="O132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P132" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q132" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R132" t="s">
         <v>74</v>
@@ -10399,10 +11040,10 @@
         <v>72</v>
       </c>
       <c r="I133">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K133">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L133" t="s">
         <v>73</v>
@@ -10414,13 +11055,13 @@
         <v>58</v>
       </c>
       <c r="O133" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P133" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q133" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R133" t="s">
         <v>74</v>
@@ -10467,10 +11108,10 @@
         <v>72</v>
       </c>
       <c r="I134">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K134">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L134" t="s">
         <v>73</v>
@@ -10482,13 +11123,13 @@
         <v>58</v>
       </c>
       <c r="O134" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P134" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q134" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R134" t="s">
         <v>74</v>
@@ -10535,10 +11176,10 @@
         <v>72</v>
       </c>
       <c r="I135">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K135">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L135" t="s">
         <v>73</v>
@@ -10550,13 +11191,13 @@
         <v>58</v>
       </c>
       <c r="O135" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P135" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q135" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R135" t="s">
         <v>74</v>
@@ -10603,10 +11244,10 @@
         <v>72</v>
       </c>
       <c r="I136">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K136">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L136" t="s">
         <v>73</v>
@@ -10618,13 +11259,13 @@
         <v>58</v>
       </c>
       <c r="O136" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P136" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q136" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R136" t="s">
         <v>74</v>
@@ -10671,10 +11312,10 @@
         <v>72</v>
       </c>
       <c r="I137">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K137">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L137" t="s">
         <v>73</v>
@@ -10686,13 +11327,13 @@
         <v>58</v>
       </c>
       <c r="O137" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P137" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R137" t="s">
         <v>74</v>
@@ -10739,10 +11380,10 @@
         <v>72</v>
       </c>
       <c r="I138">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K138">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L138" t="s">
         <v>73</v>
@@ -10754,13 +11395,13 @@
         <v>58</v>
       </c>
       <c r="O138" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P138" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R138" t="s">
         <v>74</v>
@@ -10807,10 +11448,10 @@
         <v>72</v>
       </c>
       <c r="I139">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K139">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L139" t="s">
         <v>73</v>
@@ -10822,13 +11463,13 @@
         <v>58</v>
       </c>
       <c r="O139" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P139" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q139" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R139" t="s">
         <v>74</v>
@@ -10875,10 +11516,10 @@
         <v>72</v>
       </c>
       <c r="I140">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K140">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L140" t="s">
         <v>73</v>
@@ -10890,13 +11531,13 @@
         <v>58</v>
       </c>
       <c r="O140" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P140" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q140" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R140" t="s">
         <v>74</v>
@@ -10943,10 +11584,10 @@
         <v>72</v>
       </c>
       <c r="I141">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K141">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L141" t="s">
         <v>73</v>
@@ -10958,13 +11599,13 @@
         <v>58</v>
       </c>
       <c r="O141" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P141" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q141" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R141" t="s">
         <v>74</v>
@@ -11011,10 +11652,10 @@
         <v>72</v>
       </c>
       <c r="I142">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K142">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L142" t="s">
         <v>73</v>
@@ -11026,13 +11667,13 @@
         <v>58</v>
       </c>
       <c r="O142" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P142" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q142" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R142" t="s">
         <v>74</v>
@@ -11079,10 +11720,10 @@
         <v>72</v>
       </c>
       <c r="I143">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K143">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L143" t="s">
         <v>73</v>
@@ -11094,13 +11735,13 @@
         <v>58</v>
       </c>
       <c r="O143" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P143" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q143" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R143" t="s">
         <v>74</v>
@@ -11147,10 +11788,10 @@
         <v>72</v>
       </c>
       <c r="I144">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K144">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L144" t="s">
         <v>73</v>
@@ -11162,13 +11803,13 @@
         <v>58</v>
       </c>
       <c r="O144" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P144" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q144" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R144" t="s">
         <v>74</v>
@@ -11215,10 +11856,10 @@
         <v>72</v>
       </c>
       <c r="I145">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K145">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L145" t="s">
         <v>73</v>
@@ -11230,13 +11871,13 @@
         <v>58</v>
       </c>
       <c r="O145" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P145" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q145" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R145" t="s">
         <v>74</v>
@@ -11283,10 +11924,10 @@
         <v>72</v>
       </c>
       <c r="I146">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K146">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L146" t="s">
         <v>73</v>
@@ -11298,13 +11939,13 @@
         <v>58</v>
       </c>
       <c r="O146" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P146" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q146" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R146" t="s">
         <v>74</v>
@@ -11351,10 +11992,10 @@
         <v>72</v>
       </c>
       <c r="I147">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K147">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L147" t="s">
         <v>73</v>
@@ -11366,13 +12007,13 @@
         <v>58</v>
       </c>
       <c r="O147" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P147" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q147" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R147" t="s">
         <v>74</v>
@@ -11419,10 +12060,10 @@
         <v>72</v>
       </c>
       <c r="I148">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K148">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L148" t="s">
         <v>73</v>
@@ -11434,13 +12075,13 @@
         <v>58</v>
       </c>
       <c r="O148" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P148" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q148" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R148" t="s">
         <v>74</v>
@@ -11487,10 +12128,10 @@
         <v>72</v>
       </c>
       <c r="I149">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K149">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L149" t="s">
         <v>73</v>
@@ -11502,13 +12143,13 @@
         <v>58</v>
       </c>
       <c r="O149" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P149" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q149" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R149" t="s">
         <v>74</v>
@@ -11555,10 +12196,10 @@
         <v>72</v>
       </c>
       <c r="I150">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K150">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L150" t="s">
         <v>73</v>
@@ -11570,13 +12211,13 @@
         <v>58</v>
       </c>
       <c r="O150" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P150" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q150" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R150" t="s">
         <v>74</v>
@@ -11623,10 +12264,10 @@
         <v>72</v>
       </c>
       <c r="I151">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K151">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L151" t="s">
         <v>73</v>
@@ -11638,13 +12279,13 @@
         <v>58</v>
       </c>
       <c r="O151" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P151" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q151" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R151" t="s">
         <v>74</v>
@@ -11691,10 +12332,10 @@
         <v>72</v>
       </c>
       <c r="I152">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K152">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L152" t="s">
         <v>73</v>
@@ -11706,13 +12347,13 @@
         <v>58</v>
       </c>
       <c r="O152" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P152" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q152" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R152" t="s">
         <v>74</v>
@@ -11759,10 +12400,10 @@
         <v>72</v>
       </c>
       <c r="I153">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K153">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L153" t="s">
         <v>73</v>
@@ -11774,13 +12415,13 @@
         <v>58</v>
       </c>
       <c r="O153" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P153" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q153" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R153" t="s">
         <v>74</v>
@@ -11827,10 +12468,10 @@
         <v>72</v>
       </c>
       <c r="I154">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K154">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L154" t="s">
         <v>73</v>
@@ -11842,13 +12483,13 @@
         <v>58</v>
       </c>
       <c r="O154" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P154" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q154" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R154" t="s">
         <v>74</v>
@@ -11895,10 +12536,10 @@
         <v>72</v>
       </c>
       <c r="I155">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K155">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L155" t="s">
         <v>73</v>
@@ -11910,13 +12551,13 @@
         <v>58</v>
       </c>
       <c r="O155" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P155" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q155" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R155" t="s">
         <v>74</v>
@@ -11963,10 +12604,10 @@
         <v>72</v>
       </c>
       <c r="I156">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K156">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L156" t="s">
         <v>73</v>
@@ -11978,13 +12619,13 @@
         <v>58</v>
       </c>
       <c r="O156" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P156" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q156" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R156" t="s">
         <v>74</v>
@@ -12031,10 +12672,10 @@
         <v>230</v>
       </c>
       <c r="I157">
-        <v>200.0</v>
+        <v>200</v>
       </c>
       <c r="K157">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L157" t="s">
         <v>56</v>
@@ -12046,10 +12687,10 @@
         <v>232</v>
       </c>
       <c r="O157" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P157" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q157" t="s">
         <v>233</v>
@@ -12099,10 +12740,10 @@
         <v>230</v>
       </c>
       <c r="I158">
-        <v>200.0</v>
+        <v>200</v>
       </c>
       <c r="K158">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L158" t="s">
         <v>56</v>
@@ -12114,10 +12755,10 @@
         <v>232</v>
       </c>
       <c r="O158" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P158" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q158" t="s">
         <v>233</v>
@@ -12167,10 +12808,10 @@
         <v>230</v>
       </c>
       <c r="I159">
-        <v>200.0</v>
+        <v>200</v>
       </c>
       <c r="K159">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L159" t="s">
         <v>56</v>
@@ -12182,10 +12823,10 @@
         <v>232</v>
       </c>
       <c r="O159" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P159" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q159" t="s">
         <v>233</v>
@@ -12209,7 +12850,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="160" spans="1:29">
+    <row r="160" spans="1:28">
       <c r="A160">
         <v>29</v>
       </c>
@@ -12235,7 +12876,7 @@
         <v>244</v>
       </c>
       <c r="I160">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="J160">
         <v>1</v>
@@ -12277,7 +12918,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="161" spans="1:29">
+    <row r="161" spans="1:28">
       <c r="A161">
         <v>29</v>
       </c>
@@ -12303,7 +12944,7 @@
         <v>244</v>
       </c>
       <c r="I161">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="J161">
         <v>1</v>
@@ -12345,7 +12986,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="162" spans="1:29">
+    <row r="162" spans="1:28">
       <c r="A162">
         <v>29</v>
       </c>
@@ -12371,7 +13012,7 @@
         <v>244</v>
       </c>
       <c r="I162">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -12413,7 +13054,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="163" spans="1:29">
+    <row r="163" spans="1:28">
       <c r="A163">
         <v>29</v>
       </c>
@@ -12439,7 +13080,7 @@
         <v>244</v>
       </c>
       <c r="I163">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="J163">
         <v>1</v>
@@ -12481,7 +13122,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="164" spans="1:29">
+    <row r="164" spans="1:28">
       <c r="A164">
         <v>29</v>
       </c>
@@ -12507,7 +13148,7 @@
         <v>244</v>
       </c>
       <c r="I164">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="J164">
         <v>1</v>
@@ -12549,7 +13190,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="165" spans="1:29">
+    <row r="165" spans="1:28">
       <c r="A165">
         <v>29</v>
       </c>
@@ -12575,7 +13216,7 @@
         <v>244</v>
       </c>
       <c r="I165">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="J165">
         <v>1</v>
@@ -12617,7 +13258,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="166" spans="1:29">
+    <row r="166" spans="1:28">
       <c r="A166">
         <v>29</v>
       </c>
@@ -12643,7 +13284,7 @@
         <v>244</v>
       </c>
       <c r="I166">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="J166">
         <v>1</v>
@@ -12685,7 +13326,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="167" spans="1:29">
+    <row r="167" spans="1:28">
       <c r="A167">
         <v>29</v>
       </c>
@@ -12711,7 +13352,7 @@
         <v>244</v>
       </c>
       <c r="I167">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="J167">
         <v>1</v>
@@ -12776,13 +13417,13 @@
         <v>34</v>
       </c>
       <c r="H168">
-        <v>850.0</v>
+        <v>850</v>
       </c>
       <c r="I168">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K168">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L168" t="s">
         <v>265</v>
@@ -12794,13 +13435,13 @@
         <v>232</v>
       </c>
       <c r="O168" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P168" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q168" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R168" t="s">
         <v>266</v>
@@ -12847,13 +13488,13 @@
         <v>34</v>
       </c>
       <c r="H169">
-        <v>850.0</v>
+        <v>850</v>
       </c>
       <c r="I169">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K169">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L169" t="s">
         <v>265</v>
@@ -12865,13 +13506,13 @@
         <v>232</v>
       </c>
       <c r="O169" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P169" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q169" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R169" t="s">
         <v>266</v>
@@ -12918,13 +13559,13 @@
         <v>34</v>
       </c>
       <c r="H170">
-        <v>850.0</v>
+        <v>850</v>
       </c>
       <c r="I170">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K170">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L170" t="s">
         <v>265</v>
@@ -12936,13 +13577,13 @@
         <v>232</v>
       </c>
       <c r="O170" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P170" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q170" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R170" t="s">
         <v>266</v>
@@ -13078,7 +13719,7 @@
         <v>292</v>
       </c>
       <c r="N172" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O172" t="s">
         <v>247</v>
@@ -13182,9 +13823,9 @@
         <v>298</v>
       </c>
     </row>
-    <row r="174" spans="1:29">
+    <row r="174" spans="1:17">
       <c r="A174">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B174" t="s">
         <v>306</v>
@@ -13208,10 +13849,10 @@
         <v>278</v>
       </c>
       <c r="I174">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K174">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L174" t="s">
         <v>310</v>
@@ -13223,10 +13864,10 @@
         <v>232</v>
       </c>
       <c r="O174" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P174" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q174" t="s">
         <v>249</v>
@@ -13234,7 +13875,7 @@
     </row>
     <row r="175" spans="1:29">
       <c r="A175">
-        <v>2143</v>
+        <v>29</v>
       </c>
       <c r="B175" t="s">
         <v>312</v>
@@ -13258,13 +13899,13 @@
         <v>387.9</v>
       </c>
       <c r="I175">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="J175">
         <v>2025</v>
       </c>
       <c r="K175">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="L175" t="s">
         <v>316</v>
@@ -13279,7 +13920,7 @@
         <v>247</v>
       </c>
       <c r="P175" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q175" t="s">
         <v>249</v>
@@ -13298,17 +13939,8 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>